--- a/Data/MH_EarlyNationalism.xlsx
+++ b/Data/MH_EarlyNationalism.xlsx
@@ -472,1401 +472,1397 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Which of the following leaders is known as the 'Political Guru of Gandhi'?</t>
+          <t>In which year did the Moderate Phase of the Indian National Congress end?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Tilak</t>
+          <t>1900</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Nehru</t>
+          <t>1905</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Gokhale</t>
+          <t>1910</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>R.C. Dutt</t>
+          <t>1915</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Gokhale</t>
+          <t>1905</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Gandhi referred to Gokhale as his political mentor.</t>
+          <t>The Moderates dominated until the partition of Bengal in 1905, which sparked extremist action.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>The Indian Councils Act 1892 was passed during which phase of the Congress?</t>
+          <t>Which INC session was the last one led solely by Moderates?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Extremist</t>
+          <t>1905 Banaras</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Revolutionary</t>
+          <t>1906 Calcutta</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>1907 Surat</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Post-Moderate</t>
+          <t>1904 Bombay</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>1906 Calcutta</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>The act was a result of pressure from Moderate leaders.</t>
+          <t>Next year the Surat Split occurred.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Who presided over the first session of the Indian National Congress?</t>
+          <t>The newspaper “The Hindu” was initially supportive of which phase?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>A.O. Hume</t>
+          <t>Extremist</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>W.C. Bonnerjee</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Badruddin Tyabji</t>
+          <t>Revolutionary</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Surendranath Banerjee</t>
+          <t>Gandhian</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>W.C. Bonnerjee</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Womesh Chunder Bonnerjee was the first president in Bombay session, 1885)</t>
+          <t>It published articles supporting early nationalist demands.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>The Age of Moderate Nationalism lasted from?</t>
+          <t>What was a key criticism of the Moderates by Extremists?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1885–1905</t>
+          <t>Too radical</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1885–1915</t>
+          <t>Too elitist</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1905–1920</t>
+          <t>Too cooperative with British</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1885–1947</t>
+          <t>Too revolutionary</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1885–1905</t>
+          <t>Too cooperative with British</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Before Extremist phase took over)</t>
+          <t>(They were seen as too soft and loyalist)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Which act led to the partition of Bengal in 1905?</t>
+          <t>Who among the following gave the slogan “Self-government is our birthright”?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Indian Councils Act 1892</t>
+          <t>Dadabhai Naoroji</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Morley-Minto Reforms</t>
+          <t>Gopal Krishna Gokhale</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Act of 1905</t>
+          <t>B.G. Tilak</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>There was no such act</t>
+          <t>R.C. Dutt</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>There was no such act</t>
+          <t>B.G. Tilak</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Partition was done through executive action by Lord Curzon)</t>
+          <t>This slogan was associated with the extremist movement.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Who said: "The Congress is a microscopic minority"?</t>
+          <t>Which book was written by Dadabhai Naoroji on economic drain?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Lord Curzon</t>
+          <t>India Divided</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Lord Lytton</t>
+          <t>Poverty and Un-British Rule in India</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Lord Ripon</t>
+          <t>The Problem of India</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lord Minto</t>
+          <t>Economic History of India</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lord Curzon</t>
+          <t>Poverty and Un-British Rule in India</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Justifying repressive measures and Bengal Partition)</t>
+          <t>(Seminal work explaining British economic exploitation)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Which slogan is attributed to Bal Gangadhar Tilak?</t>
+          <t>Who was elected President of INC in 1907 Surat session?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Jai Hind</t>
+          <t>Tilak</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Inquilab Zindabad</t>
+          <t>Lajpat Rai</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Swaraj is my birthright and I shall have it</t>
+          <t>Rash Behari Bose</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Do or Die</t>
+          <t>Rash Behari Ghosh</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Swaraj is my birthright and I shall have it</t>
+          <t>Rash Behari Ghosh</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Powerful assertion of self-rule)</t>
+          <t>(Moderates chose him, leading to split)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Which newspaper was started by Bal Gangadhar Tilak?</t>
+          <t>Who wrote the book ‘Poverty and Un-British Rule in India’?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kesari</t>
+          <t>Gokhale</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>The Hindu</t>
+          <t>Naoroji</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Amrita Bazar Patrika</t>
+          <t>Dutt</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Young India</t>
+          <t>Banerjee</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Kesari</t>
+          <t>Naoroji</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Tilak started ‘Kesari’ in Marathi to promote nationalism.</t>
+          <t>It argued that British policies were causing Indian poverty.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Which of the following was the main demand of early nationalists?</t>
+          <t>What was the main objective of the early nationalists?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Home Rule</t>
+          <t>Complete Independence</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Swaraj</t>
+          <t>Armed Revolution</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dominion Status</t>
+          <t>Constitutional Reforms</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Administrative and Economic Reforms</t>
+          <t>Social Reforms</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Administrative and Economic Reforms</t>
+          <t>Constitutional Reforms</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Early focus was on reforms, not independence)</t>
+          <t>(They believed in gradual reforms and dialogue)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Which of the following Moderate leaders was also a social reformer?</t>
+          <t>Which act led to the partition of Bengal in 1905?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Dadabhai Naoroji</t>
+          <t>Indian Councils Act 1892</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Gokhale</t>
+          <t>Morley-Minto Reforms</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Tilak</t>
+          <t>Act of 1905</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bipin Chandra Pal</t>
+          <t>There was no such act</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Gokhale</t>
+          <t>There was no such act</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Strong believer in social service and upliftment)</t>
+          <t>(Partition was done through executive action by Lord Curzon)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Who among these was both a Moderate and later associated with Gandhian politics?</t>
+          <t>Who coined the term "Drain of Wealth"?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tilak</t>
+          <t>A.O. Hume</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Naoroji</t>
+          <t>R.C. Dutt</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Gokhale</t>
+          <t>Gopal Krishna Gokhale</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bipin Chandra Pal</t>
+          <t>Dadabhai Naoroji</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Gokhale</t>
+          <t>Dadabhai Naoroji</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>He bridged the gap between Moderates and Gandhian politics.</t>
+          <t>He explained how British economic policies led to economic exploitation of India.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Which method was not used by the Moderates?</t>
+          <t>Which newspaper was started by Gokhale to voice nationalist ideas?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Petitions</t>
+          <t>The Hindu</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Pamphlets</t>
+          <t>The Leader</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Prayers</t>
+          <t>The Times of India</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Violent protests</t>
+          <t>Young India</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Violent protests</t>
+          <t>The Leader</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Moderates strictly avoided violence.</t>
+          <t>(He used it to advocate reforms and educate people)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Who among these was NOT a Moderate leader?</t>
+          <t>Who said “The Congress is in reality a civil war without arms”?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Dadabhai Naoroji</t>
+          <t>Lala Lajpat Rai</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Gopal Krishna Gokhale</t>
+          <t>Tilak</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Lala Lajpat Rai</t>
+          <t>Lord Curzon</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>W.C. Bonnerjee</t>
+          <t>Gokhale</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lala Lajpat Rai</t>
+          <t>Lord Curzon</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(He was part of the Extremist trio)</t>
+          <t>He criticized the Congress for creating unrest.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Who founded the ‘Servants of India Society’?</t>
+          <t>Which session saw the demand for Swaraj for the first time?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Dadabhai Naoroji</t>
+          <t>1905 Banaras</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Gopal Krishna Gokhale</t>
+          <t>1906 Calcutta</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Lala Lajpat Rai</t>
+          <t>1907 Surat</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tilak</t>
+          <t>1916 Lucknow</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Gopal Krishna Gokhale</t>
+          <t>1906 Calcutta</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>He founded it to train national workers.</t>
+          <t>This session under Dadabhai Naoroji declared Swaraj as the goal.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Who started the newspaper 'Kesari'?</t>
+          <t>Which of the following leaders is known as the 'Political Guru of Gandhi'?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Gopal Krishna Gokhale</t>
+          <t>Tilak</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Bipin Chandra Pal</t>
+          <t>Nehru</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bal Gangadhar Tilak</t>
+          <t>Gokhale</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Surendranath Banerjee</t>
+          <t>R.C. Dutt</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bal Gangadhar Tilak</t>
+          <t>Gokhale</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Used it to awaken political consciousness)</t>
+          <t>Gandhi referred to Gokhale as his political mentor.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Who among the following was not a Moderate leader?</t>
+          <t>What was the venue of the second session of the Indian National Congress?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Surendranath Banerjee</t>
+          <t>Bombay</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Gopal Krishna Gokhale</t>
+          <t>Madras</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Bal Gangadhar Tilak</t>
+          <t>Calcutta</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>M.G. Ranade</t>
+          <t>Allahabad</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bal Gangadhar Tilak</t>
+          <t>Calcutta</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Tilak was a prominent extremist leader.</t>
+          <t>(Held in 1886 and presided over by Dadabhai Naoroji)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Which event led to the rise of Extremist politics?</t>
+          <t>The term 'Moderates' in Indian politics refers to?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Partition of Bengal</t>
+          <t>Extremists</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Swadeshi Movement</t>
+          <t>British loyalists</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Rowlatt Act</t>
+          <t>Early Nationalists</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Simon Commission</t>
+          <t>Revolutionaries</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Partition of Bengal</t>
+          <t>Early Nationalists</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>It was the spark that turned public sentiment radical.</t>
+          <t>(They adopted peaceful and constitutional methods)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Which newspaper was started by Gokhale to voice nationalist ideas?</t>
+          <t>Who among the following founded the 'Servants of India Society'?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>The Hindu</t>
+          <t>Dadabhai Naoroji</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>The Leader</t>
+          <t>Gopal Krishna Gokhale</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>The Times of India</t>
+          <t>Tilak</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Young India</t>
+          <t>D.E. Wacha</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>The Leader</t>
+          <t>Gopal Krishna Gokhale</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(He used it to advocate reforms and educate people)</t>
+          <t>(Founded in 1905 for education and social service)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>The trio of Lal-Bal-Pal belonged to which group?</t>
+          <t>Which British officer played a key role in the foundation of INC?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Moderates</t>
+          <t>Lord Ripon</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Extremists</t>
+          <t>Lord Dufferin</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Revolutionaries</t>
+          <t>A.O. Hume</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Socialists</t>
+          <t>Sir John Lawrence</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Extremists</t>
+          <t>A.O. Hume</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Assertive nationalists for self-rule)</t>
+          <t>(Retired ICS officer who helped Indians unite politically)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Who is considered the father of Indian National Congress?</t>
+          <t>Which Moderate leader was known as the “Grand Old Man of India”?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>A.O. Hume</t>
+          <t>Gokhale</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Dadabhai Naoroji</t>
+          <t>Dutt</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Gopal Krishna Gokhale</t>
+          <t>Naoroji</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Surendranath Banerjee</t>
+          <t>Tilak</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>A.O. Hume</t>
+          <t>Naoroji</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>He was the British civil servant who played a major role in founding the INC in 1885.</t>
+          <t>He was one of the oldest and most respected leaders.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>What was the venue of the second session of the Indian National Congress?</t>
+          <t>Which slogan is attributed to Bal Gangadhar Tilak?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bombay</t>
+          <t>Jai Hind</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Madras</t>
+          <t>Inquilab Zindabad</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Calcutta</t>
+          <t>Swaraj is my birthright and I shall have it</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Allahabad</t>
+          <t>Do or Die</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Calcutta</t>
+          <t>Swaraj is my birthright and I shall have it</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Held in 1886 and presided over by Dadabhai Naoroji)</t>
+          <t>(Powerful assertion of self-rule)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Which book was written by Dadabhai Naoroji on economic drain?</t>
+          <t>The trio of Lal-Bal-Pal belonged to which group?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>India Divided</t>
+          <t>Moderates</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Poverty and Un-British Rule in India</t>
+          <t>Extremists</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>The Problem of India</t>
+          <t>Revolutionaries</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Economic History of India</t>
+          <t>Socialists</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poverty and Un-British Rule in India</t>
+          <t>Extremists</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Seminal work explaining British economic exploitation)</t>
+          <t>(Assertive nationalists for self-rule)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Who wrote the book ‘Poverty and Un-British Rule in India’?</t>
+          <t>Which of the following was not a demand of the Moderates?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Gokhale</t>
+          <t>Expansion of legislative councils</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Naoroji</t>
+          <t>Separation of judiciary and executive</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Dutt</t>
+          <t>Complete independence</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Banerjee</t>
+          <t>Reduction in military expenditure</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Naoroji</t>
+          <t>Complete independence</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>It argued that British policies were causing Indian poverty.</t>
+          <t>Moderates sought reforms, not independence.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Which session of the INC was presided over by Dadabhai Naoroji for the first time?</t>
+          <t>Who among these was NOT a Moderate leader?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Bombay 1885</t>
+          <t>Dadabhai Naoroji</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Calcutta 1886</t>
+          <t>Gopal Krishna Gokhale</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Madras 1887</t>
+          <t>Lala Lajpat Rai</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Allahabad 1888</t>
+          <t>W.C. Bonnerjee</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Calcutta 1886</t>
+          <t>Lala Lajpat Rai</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Dadabhai Naoroji presided over the second session of INC in 1886.</t>
+          <t>(He was part of the Extremist trio)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Who was elected President of INC in 1907 Surat session?</t>
+          <t>Which of these demands was first raised by the Moderates?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Tilak</t>
+          <t>Swaraj</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Lajpat Rai</t>
+          <t>Universal Adult Franchise</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Rash Behari Bose</t>
+          <t>Indianisation of Civil Services</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rash Behari Ghosh</t>
+          <t>Boycott of British Goods</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Rash Behari Ghosh</t>
+          <t>Indianisation of Civil Services</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Moderates chose him, leading to split)</t>
+          <t>Moderates demanded ICS entry for Indians.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>In which session was the demand for 'Swaraj' first made by INC?</t>
+          <t>The term “Economic Critique of British Imperialism” is associated with:</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1906 Calcutta</t>
+          <t>Extremists</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1907 Surat</t>
+          <t>Moderates</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1916 Lucknow</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>1920 Nagpur</t>
-        </is>
-      </c>
+          <t>Revolutionaries</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>1906 Calcutta</t>
+          <t>Moderates</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Presided by Dadabhai Naoroji; Swaraj was formally adopted)</t>
+          <t>They exposed British economic exploitation through data and speeches.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Who coined the term "Drain of Wealth"?</t>
+          <t>Which event led to the rise of Extremist politics?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>A.O. Hume</t>
+          <t>Partition of Bengal</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>R.C. Dutt</t>
+          <t>Swadeshi Movement</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Gopal Krishna Gokhale</t>
+          <t>Rowlatt Act</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dadabhai Naoroji</t>
+          <t>Simon Commission</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dadabhai Naoroji</t>
+          <t>Partition of Bengal</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>He explained how British economic policies led to economic exploitation of India.</t>
+          <t>It was the spark that turned public sentiment radical.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Who among the following exposed the 'Drain of Wealth' theory?</t>
+          <t>Which session of the INC was presided over by Dadabhai Naoroji for the first time?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Bal Gangadhar Tilak</t>
+          <t>Bombay 1885</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Dadabhai Naoroji</t>
+          <t>Calcutta 1886</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Gopal Krishna Gokhale</t>
+          <t>Madras 1887</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>M.G. Ranade</t>
+          <t>Allahabad 1888</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dadabhai Naoroji</t>
+          <t>Calcutta 1886</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(He argued British rule drained India’s resources to Britain)</t>
+          <t>Dadabhai Naoroji presided over the second session of INC in 1886.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Which of the following was not a demand of the Moderates?</t>
+          <t>Who is considered the father of Indian National Congress?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Expansion of legislative councils</t>
+          <t>A.O. Hume</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Separation of judiciary and executive</t>
+          <t>Dadabhai Naoroji</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Complete independence</t>
+          <t>Gopal Krishna Gokhale</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Reduction in military expenditure</t>
+          <t>Surendranath Banerjee</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Complete independence</t>
+          <t>A.O. Hume</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Moderates sought reforms, not independence.</t>
+          <t>He was the British civil servant who played a major role in founding the INC in 1885.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Which Congress session saw the Moderates and Extremists split?</t>
+          <t>Who started the newspaper 'Kesari'?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1905</t>
+          <t>Gopal Krishna Gokhale</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1906</t>
+          <t>Bipin Chandra Pal</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1907</t>
+          <t>Bal Gangadhar Tilak</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1908</t>
+          <t>Surendranath Banerjee</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>1907</t>
+          <t>Bal Gangadhar Tilak</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Split occurred at Surat session due to ideological differences)</t>
+          <t>(Used it to awaken political consciousness)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>What was a key criticism of the Moderates by Extremists?</t>
+          <t>Which method was not used by the Moderates?</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Too radical</t>
+          <t>Petitions</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Too elitist</t>
+          <t>Pamphlets</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Too cooperative with British</t>
+          <t>Prayers</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Too revolutionary</t>
+          <t>Violent protests</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Too cooperative with British</t>
+          <t>Violent protests</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(They were seen as too soft and loyalist)</t>
+          <t>Moderates strictly avoided violence.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Who was called the 'Political Guru' of Gandhi?</t>
+          <t>Which newspaper was started by Bal Gangadhar Tilak?</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Tilak</t>
+          <t>Kesari</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Nehru</t>
+          <t>The Hindu</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Gokhale</t>
+          <t>Amrita Bazar Patrika</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lala Lajpat Rai</t>
+          <t>Young India</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Gokhale</t>
+          <t>Kesari</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(He mentored Gandhi in his early political life)</t>
+          <t>Tilak started ‘Kesari’ in Marathi to promote nationalism.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>In which year did the Moderate Phase of the Indian National Congress end?</t>
+          <t>Which of the following was the main demand of early nationalists?</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>Home Rule</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1905</t>
+          <t>Swaraj</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1910</t>
+          <t>Dominion Status</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>1915</t>
+          <t>Administrative and Economic Reforms</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>1905</t>
+          <t>Administrative and Economic Reforms</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>The Moderates dominated until the partition of Bengal in 1905, which sparked extremist action.</t>
+          <t>(Early focus was on reforms, not independence)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>The Indian National Congress was founded in which year?</t>
+          <t>Who among the following exposed the 'Drain of Wealth' theory?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1885</t>
+          <t>Bal Gangadhar Tilak</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1895</t>
+          <t>Dadabhai Naoroji</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1905</t>
+          <t>Gopal Krishna Gokhale</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>1875</t>
+          <t>M.G. Ranade</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>1885</t>
+          <t>Dadabhai Naoroji</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Founded in 1885 by A.O. Hume to create a platform for civil and political dialogue)</t>
+          <t>(He argued British rule drained India’s resources to Britain)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Who said “The Congress is in reality a civil war without arms”?</t>
+          <t>Who was called the 'Political Guru' of Gandhi?</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
+          <t>Tilak</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Nehru</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Gokhale</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
           <t>Lala Lajpat Rai</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Tilak</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Lord Curzon</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>Gokhale</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Lord Curzon</t>
-        </is>
-      </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>He criticized the Congress for creating unrest.</t>
+          <t>(He mentored Gandhi in his early political life)</t>
         </is>
       </c>
     </row>
@@ -1876,47 +1872,47 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Who among the following founded the 'Servants of India Society'?</t>
+          <t>The Indian Councils Act 1892 was passed during which phase of the Congress?</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Dadabhai Naoroji</t>
+          <t>Extremist</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Gopal Krishna Gokhale</t>
+          <t>Revolutionary</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Tilak</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>D.E. Wacha</t>
+          <t>Post-Moderate</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Gopal Krishna Gokhale</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Founded in 1905 for education and social service)</t>
+          <t>The act was a result of pressure from Moderate leaders.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Who is known as the 'Father of Indian Nationalism'?</t>
+          <t>Which of the following Moderate leaders was also a social reformer?</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1926,67 +1922,67 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Gopal Krishna Gokhale</t>
+          <t>Gokhale</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Bal Gangadhar Tilak</t>
+          <t>Tilak</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>A.O. Hume</t>
+          <t>Bipin Chandra Pal</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dadabhai Naoroji</t>
+          <t>Gokhale</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Recognized for pioneering efforts in forming INC and economic critique of British rule)</t>
+          <t>(Strong believer in social service and upliftment)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Which of these demands was first raised by the Moderates?</t>
+          <t>Who founded the ‘Servants of India Society’?</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Swaraj</t>
+          <t>Dadabhai Naoroji</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Universal Adult Franchise</t>
+          <t>Gopal Krishna Gokhale</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Indianisation of Civil Services</t>
+          <t>Lala Lajpat Rai</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Boycott of British Goods</t>
+          <t>Tilak</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Indianisation of Civil Services</t>
+          <t>Gopal Krishna Gokhale</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Moderates demanded ICS entry for Indians.</t>
+          <t>He founded it to train national workers.</t>
         </is>
       </c>
     </row>
@@ -2032,397 +2028,401 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Who among the following gave the slogan “Self-government is our birthright”?</t>
+          <t>The Age of Moderate Nationalism lasted from?</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Dadabhai Naoroji</t>
+          <t>1885–1905</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Gopal Krishna Gokhale</t>
+          <t>1885–1915</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>B.G. Tilak</t>
+          <t>1905–1920</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>R.C. Dutt</t>
+          <t>1885–1947</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>B.G. Tilak</t>
+          <t>1885–1905</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>This slogan was associated with the extremist movement.</t>
+          <t>(Before Extremist phase took over)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>The newspaper “The Hindu” was initially supportive of which phase?</t>
+          <t>Who among these was both a Moderate and later associated with Gandhian politics?</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Extremist</t>
+          <t>Tilak</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Naoroji</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Revolutionary</t>
+          <t>Gokhale</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gandhian</t>
+          <t>Bipin Chandra Pal</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Gokhale</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>It published articles supporting early nationalist demands.</t>
+          <t>He bridged the gap between Moderates and Gandhian politics.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Which Moderate leader was known as the “Grand Old Man of India”?</t>
+          <t>In which session was the demand for 'Swaraj' first made by INC?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Gokhale</t>
+          <t>1906 Calcutta</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Dutt</t>
+          <t>1907 Surat</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Naoroji</t>
+          <t>1916 Lucknow</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tilak</t>
+          <t>1920 Nagpur</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Naoroji</t>
+          <t>1906 Calcutta</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>He was one of the oldest and most respected leaders.</t>
+          <t>(Presided by Dadabhai Naoroji; Swaraj was formally adopted)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>What was the main focus of early nationalism?</t>
+          <t>Who presided over the first session of the Indian National Congress?</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Religious reforms</t>
+          <t>A.O. Hume</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Social service</t>
+          <t>W.C. Bonnerjee</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Political reforms</t>
+          <t>Badruddin Tyabji</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Armed rebellion</t>
+          <t>Surendranath Banerjee</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Political reforms</t>
+          <t>W.C. Bonnerjee</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Moderates focused on constitutional and political demands.</t>
+          <t>(Womesh Chunder Bonnerjee was the first president in Bombay session, 1885)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>What was the main objective of the early nationalists?</t>
+          <t>The Indian National Congress was founded in which year?</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Complete Independence</t>
+          <t>1885</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Armed Revolution</t>
+          <t>1895</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Constitutional Reforms</t>
+          <t>1905</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Social Reforms</t>
+          <t>1875</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Constitutional Reforms</t>
+          <t>1885</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(They believed in gradual reforms and dialogue)</t>
+          <t>(Founded in 1885 by A.O. Hume to create a platform for civil and political dialogue)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Which INC session was the last one led solely by Moderates?</t>
+          <t>Which Congress session saw the Moderates and Extremists split?</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>1905 Banaras</t>
+          <t>1905</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1906 Calcutta</t>
+          <t>1906</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1907 Surat</t>
+          <t>1907</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>1904 Bombay</t>
+          <t>1908</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>1906 Calcutta</t>
+          <t>1907</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Next year the Surat Split occurred.</t>
+          <t>(Split occurred at Surat session due to ideological differences)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Which session saw the demand for Swaraj for the first time?</t>
+          <t>Who among the following was not a Moderate leader?</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>1905 Banaras</t>
+          <t>Surendranath Banerjee</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1906 Calcutta</t>
+          <t>Gopal Krishna Gokhale</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1907 Surat</t>
+          <t>Bal Gangadhar Tilak</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>1916 Lucknow</t>
+          <t>M.G. Ranade</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>1906 Calcutta</t>
+          <t>Bal Gangadhar Tilak</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>This session under Dadabhai Naoroji declared Swaraj as the goal.</t>
+          <t>Tilak was a prominent extremist leader.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Which British officer played a key role in the foundation of INC?</t>
+          <t>Who said: "The Congress is a microscopic minority"?</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
+          <t>Lord Curzon</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Lord Lytton</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
           <t>Lord Ripon</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Lord Dufferin</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>A.O. Hume</t>
-        </is>
-      </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Sir John Lawrence</t>
+          <t>Lord Minto</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>A.O. Hume</t>
+          <t>Lord Curzon</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Retired ICS officer who helped Indians unite politically)</t>
+          <t>(Justifying repressive measures and Bengal Partition)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>The term “Economic Critique of British Imperialism” is associated with:</t>
+          <t>What was the main focus of early nationalism?</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Extremists</t>
+          <t>Religious reforms</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Moderates</t>
+          <t>Social service</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Revolutionaries</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr"/>
+          <t>Political reforms</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Armed rebellion</t>
+        </is>
+      </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Moderates</t>
+          <t>Political reforms</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>They exposed British economic exploitation through data and speeches.</t>
+          <t>Moderates focused on constitutional and political demands.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>The term 'Moderates' in Indian politics refers to?</t>
+          <t>Who is known as the 'Father of Indian Nationalism'?</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Extremists</t>
+          <t>Dadabhai Naoroji</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>British loyalists</t>
+          <t>Gopal Krishna Gokhale</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Early Nationalists</t>
+          <t>Bal Gangadhar Tilak</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Revolutionaries</t>
+          <t>A.O. Hume</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Early Nationalists</t>
+          <t>Dadabhai Naoroji</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(They adopted peaceful and constitutional methods)</t>
+          <t>(Recognized for pioneering efforts in forming INC and economic critique of British rule)</t>
         </is>
       </c>
     </row>

--- a/Data/MH_EarlyNationalism.xlsx
+++ b/Data/MH_EarlyNationalism.xlsx
@@ -472,171 +472,167 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>In which year did the Moderate Phase of the Indian National Congress end?</t>
+          <t>Which of the following leaders is known as the 'Political Guru of Gandhi'?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>Tilak</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1905</t>
+          <t>Nehru</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1910</t>
+          <t>Gokhale</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1915</t>
+          <t>R.C. Dutt</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1905</t>
+          <t>Gokhale</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>The Moderates dominated until the partition of Bengal in 1905, which sparked extremist action.</t>
+          <t>Gandhi referred to Gokhale as his political mentor.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Which INC session was the last one led solely by Moderates?</t>
+          <t>The term “Economic Critique of British Imperialism” is associated with:</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1905 Banaras</t>
+          <t>Extremists</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1906 Calcutta</t>
+          <t>Moderates</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1907 Surat</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>1904 Bombay</t>
-        </is>
-      </c>
+          <t>Revolutionaries</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1906 Calcutta</t>
+          <t>Moderates</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Next year the Surat Split occurred.</t>
+          <t>They exposed British economic exploitation through data and speeches.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>The newspaper “The Hindu” was initially supportive of which phase?</t>
+          <t>Who among these was both a Moderate and later associated with Gandhian politics?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Extremist</t>
+          <t>Tilak</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Naoroji</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Revolutionary</t>
+          <t>Gokhale</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gandhian</t>
+          <t>Bipin Chandra Pal</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Gokhale</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>It published articles supporting early nationalist demands.</t>
+          <t>He bridged the gap between Moderates and Gandhian politics.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>What was a key criticism of the Moderates by Extremists?</t>
+          <t>Which book was written by Dadabhai Naoroji on economic drain?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Too radical</t>
+          <t>India Divided</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Too elitist</t>
+          <t>Poverty and Un-British Rule in India</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Too cooperative with British</t>
+          <t>The Problem of India</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Too revolutionary</t>
+          <t>Economic History of India</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Too cooperative with British</t>
+          <t>Poverty and Un-British Rule in India</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(They were seen as too soft and loyalist)</t>
+          <t>(Seminal work explaining British economic exploitation)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Who among the following gave the slogan “Self-government is our birthright”?</t>
+          <t>Who among the following founded the 'Servants of India Society'?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -651,222 +647,222 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>B.G. Tilak</t>
+          <t>Tilak</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>R.C. Dutt</t>
+          <t>D.E. Wacha</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>B.G. Tilak</t>
+          <t>Gopal Krishna Gokhale</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>This slogan was associated with the extremist movement.</t>
+          <t>(Founded in 1905 for education and social service)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Which book was written by Dadabhai Naoroji on economic drain?</t>
+          <t>Which event led to the rise of Extremist politics?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>India Divided</t>
+          <t>Partition of Bengal</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Poverty and Un-British Rule in India</t>
+          <t>Swadeshi Movement</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>The Problem of India</t>
+          <t>Rowlatt Act</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Economic History of India</t>
+          <t>Simon Commission</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poverty and Un-British Rule in India</t>
+          <t>Partition of Bengal</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Seminal work explaining British economic exploitation)</t>
+          <t>It was the spark that turned public sentiment radical.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Who was elected President of INC in 1907 Surat session?</t>
+          <t>Who presided over the first session of the Indian National Congress?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tilak</t>
+          <t>A.O. Hume</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Lajpat Rai</t>
+          <t>W.C. Bonnerjee</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Rash Behari Bose</t>
+          <t>Badruddin Tyabji</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rash Behari Ghosh</t>
+          <t>Surendranath Banerjee</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rash Behari Ghosh</t>
+          <t>W.C. Bonnerjee</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Moderates chose him, leading to split)</t>
+          <t>(Womesh Chunder Bonnerjee was the first president in Bombay session, 1885)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Who wrote the book ‘Poverty and Un-British Rule in India’?</t>
+          <t>Which of the following Moderate leaders was also a social reformer?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>Dadabhai Naoroji</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
           <t>Gokhale</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Naoroji</t>
-        </is>
-      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dutt</t>
+          <t>Tilak</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Banerjee</t>
+          <t>Bipin Chandra Pal</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Naoroji</t>
+          <t>Gokhale</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>It argued that British policies were causing Indian poverty.</t>
+          <t>(Strong believer in social service and upliftment)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>What was the main objective of the early nationalists?</t>
+          <t>The trio of Lal-Bal-Pal belonged to which group?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Complete Independence</t>
+          <t>Moderates</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Armed Revolution</t>
+          <t>Extremists</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Constitutional Reforms</t>
+          <t>Revolutionaries</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Social Reforms</t>
+          <t>Socialists</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Constitutional Reforms</t>
+          <t>Extremists</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(They believed in gradual reforms and dialogue)</t>
+          <t>(Assertive nationalists for self-rule)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Which act led to the partition of Bengal in 1905?</t>
+          <t>Who said “The Congress is in reality a civil war without arms”?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Indian Councils Act 1892</t>
+          <t>Lala Lajpat Rai</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Morley-Minto Reforms</t>
+          <t>Tilak</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Act of 1905</t>
+          <t>Lord Curzon</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>There was no such act</t>
+          <t>Gokhale</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>There was no such act</t>
+          <t>Lord Curzon</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Partition was done through executive action by Lord Curzon)</t>
+          <t>He criticized the Congress for creating unrest.</t>
         </is>
       </c>
     </row>
@@ -912,1492 +908,1496 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Which newspaper was started by Gokhale to voice nationalist ideas?</t>
+          <t>Who founded the ‘Servants of India Society’?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>The Hindu</t>
+          <t>Dadabhai Naoroji</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>The Leader</t>
+          <t>Gopal Krishna Gokhale</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>The Times of India</t>
+          <t>Lala Lajpat Rai</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Young India</t>
+          <t>Tilak</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>The Leader</t>
+          <t>Gopal Krishna Gokhale</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(He used it to advocate reforms and educate people)</t>
+          <t>He founded it to train national workers.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Who said “The Congress is in reality a civil war without arms”?</t>
+          <t>Who wrote the book ‘Poverty and Un-British Rule in India’?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Lala Lajpat Rai</t>
+          <t>Gokhale</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Tilak</t>
+          <t>Naoroji</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Lord Curzon</t>
+          <t>Dutt</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gokhale</t>
+          <t>Banerjee</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lord Curzon</t>
+          <t>Naoroji</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>He criticized the Congress for creating unrest.</t>
+          <t>It argued that British policies were causing Indian poverty.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Which session saw the demand for Swaraj for the first time?</t>
+          <t>Which act led to the partition of Bengal in 1905?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1905 Banaras</t>
+          <t>Indian Councils Act 1892</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1906 Calcutta</t>
+          <t>Morley-Minto Reforms</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1907 Surat</t>
+          <t>Act of 1905</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1916 Lucknow</t>
+          <t>There was no such act</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1906 Calcutta</t>
+          <t>There was no such act</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>This session under Dadabhai Naoroji declared Swaraj as the goal.</t>
+          <t>(Partition was done through executive action by Lord Curzon)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Which of the following leaders is known as the 'Political Guru of Gandhi'?</t>
+          <t>In which year did the Moderate Phase of the Indian National Congress end?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tilak</t>
+          <t>1900</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Nehru</t>
+          <t>1905</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Gokhale</t>
+          <t>1910</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>R.C. Dutt</t>
+          <t>1915</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Gokhale</t>
+          <t>1905</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Gandhi referred to Gokhale as his political mentor.</t>
+          <t>The Moderates dominated until the partition of Bengal in 1905, which sparked extremist action.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>What was the venue of the second session of the Indian National Congress?</t>
+          <t>Who was elected President of INC in 1907 Surat session?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bombay</t>
+          <t>Tilak</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Madras</t>
+          <t>Lajpat Rai</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Calcutta</t>
+          <t>Rash Behari Bose</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Allahabad</t>
+          <t>Rash Behari Ghosh</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Calcutta</t>
+          <t>Rash Behari Ghosh</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Held in 1886 and presided over by Dadabhai Naoroji)</t>
+          <t>(Moderates chose him, leading to split)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>The term 'Moderates' in Indian politics refers to?</t>
+          <t>Who among the following gave the slogan “Self-government is our birthright”?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Extremists</t>
+          <t>Dadabhai Naoroji</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>British loyalists</t>
+          <t>Gopal Krishna Gokhale</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Early Nationalists</t>
+          <t>B.G. Tilak</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Revolutionaries</t>
+          <t>R.C. Dutt</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Early Nationalists</t>
+          <t>B.G. Tilak</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(They adopted peaceful and constitutional methods)</t>
+          <t>This slogan was associated with the extremist movement.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Who among the following founded the 'Servants of India Society'?</t>
+          <t>Which of the following was the main limitation of the Moderate phase?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Dadabhai Naoroji</t>
+          <t>Lack of organization</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Gopal Krishna Gokhale</t>
+          <t>Use of violence</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Tilak</t>
+          <t>Support from peasants</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>D.E. Wacha</t>
+          <t>Strong press</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Gopal Krishna Gokhale</t>
+          <t>Lack of organization</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Founded in 1905 for education and social service)</t>
+          <t>Their peaceful methods lacked mass mobilization.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Which British officer played a key role in the foundation of INC?</t>
+          <t>Who is considered the father of Indian National Congress?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Lord Ripon</t>
+          <t>A.O. Hume</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Lord Dufferin</t>
+          <t>Dadabhai Naoroji</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
+          <t>Gopal Krishna Gokhale</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Surendranath Banerjee</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
           <t>A.O. Hume</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Sir John Lawrence</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>A.O. Hume</t>
-        </is>
-      </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Retired ICS officer who helped Indians unite politically)</t>
+          <t>He was the British civil servant who played a major role in founding the INC in 1885.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Which Moderate leader was known as the “Grand Old Man of India”?</t>
+          <t>Which of these demands was first raised by the Moderates?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Gokhale</t>
+          <t>Swaraj</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Dutt</t>
+          <t>Universal Adult Franchise</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Naoroji</t>
+          <t>Indianisation of Civil Services</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tilak</t>
+          <t>Boycott of British Goods</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Naoroji</t>
+          <t>Indianisation of Civil Services</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>He was one of the oldest and most respected leaders.</t>
+          <t>Moderates demanded ICS entry for Indians.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Which slogan is attributed to Bal Gangadhar Tilak?</t>
+          <t>What was the main objective of the early nationalists?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Jai Hind</t>
+          <t>Complete Independence</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Inquilab Zindabad</t>
+          <t>Armed Revolution</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Swaraj is my birthright and I shall have it</t>
+          <t>Constitutional Reforms</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Do or Die</t>
+          <t>Social Reforms</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Swaraj is my birthright and I shall have it</t>
+          <t>Constitutional Reforms</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Powerful assertion of self-rule)</t>
+          <t>(They believed in gradual reforms and dialogue)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>The trio of Lal-Bal-Pal belonged to which group?</t>
+          <t>The Age of Moderate Nationalism lasted from?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Moderates</t>
+          <t>1885–1905</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Extremists</t>
+          <t>1885–1915</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Revolutionaries</t>
+          <t>1905–1920</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Socialists</t>
+          <t>1885–1947</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Extremists</t>
+          <t>1885–1905</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Assertive nationalists for self-rule)</t>
+          <t>(Before Extremist phase took over)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Which of the following was not a demand of the Moderates?</t>
+          <t>Who was called the 'Political Guru' of Gandhi?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Expansion of legislative councils</t>
+          <t>Tilak</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Separation of judiciary and executive</t>
+          <t>Nehru</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Complete independence</t>
+          <t>Gokhale</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Reduction in military expenditure</t>
+          <t>Lala Lajpat Rai</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Complete independence</t>
+          <t>Gokhale</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Moderates sought reforms, not independence.</t>
+          <t>(He mentored Gandhi in his early political life)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Who among these was NOT a Moderate leader?</t>
+          <t>Which newspaper was started by Gokhale to voice nationalist ideas?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Dadabhai Naoroji</t>
+          <t>The Hindu</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Gopal Krishna Gokhale</t>
+          <t>The Leader</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Lala Lajpat Rai</t>
+          <t>The Times of India</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>W.C. Bonnerjee</t>
+          <t>Young India</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lala Lajpat Rai</t>
+          <t>The Leader</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(He was part of the Extremist trio)</t>
+          <t>(He used it to advocate reforms and educate people)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Which of these demands was first raised by the Moderates?</t>
+          <t>Which session of the INC was presided over by Dadabhai Naoroji for the first time?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Swaraj</t>
+          <t>Bombay 1885</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Universal Adult Franchise</t>
+          <t>Calcutta 1886</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Indianisation of Civil Services</t>
+          <t>Madras 1887</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Boycott of British Goods</t>
+          <t>Allahabad 1888</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Indianisation of Civil Services</t>
+          <t>Calcutta 1886</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Moderates demanded ICS entry for Indians.</t>
+          <t>Dadabhai Naoroji presided over the second session of INC in 1886.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>The term “Economic Critique of British Imperialism” is associated with:</t>
+          <t>The newspaper “The Hindu” was initially supportive of which phase?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Extremists</t>
+          <t>Extremist</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Moderates</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Revolutionaries</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr"/>
+          <t>Revolutionary</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Gandhian</t>
+        </is>
+      </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Moderates</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>They exposed British economic exploitation through data and speeches.</t>
+          <t>It published articles supporting early nationalist demands.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Which event led to the rise of Extremist politics?</t>
+          <t>The Indian Councils Act 1892 was passed during which phase of the Congress?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Partition of Bengal</t>
+          <t>Extremist</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Swadeshi Movement</t>
+          <t>Revolutionary</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Rowlatt Act</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Simon Commission</t>
+          <t>Post-Moderate</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Partition of Bengal</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>It was the spark that turned public sentiment radical.</t>
+          <t>The act was a result of pressure from Moderate leaders.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Which session of the INC was presided over by Dadabhai Naoroji for the first time?</t>
+          <t>What was the venue of the second session of the Indian National Congress?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Bombay 1885</t>
+          <t>Bombay</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Calcutta 1886</t>
+          <t>Madras</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Madras 1887</t>
+          <t>Calcutta</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Allahabad 1888</t>
+          <t>Allahabad</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Calcutta 1886</t>
+          <t>Calcutta</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Dadabhai Naoroji presided over the second session of INC in 1886.</t>
+          <t>(Held in 1886 and presided over by Dadabhai Naoroji)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Who is considered the father of Indian National Congress?</t>
+          <t>Which method was not used by the Moderates?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>A.O. Hume</t>
+          <t>Petitions</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Dadabhai Naoroji</t>
+          <t>Pamphlets</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Gopal Krishna Gokhale</t>
+          <t>Prayers</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Surendranath Banerjee</t>
+          <t>Violent protests</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>A.O. Hume</t>
+          <t>Violent protests</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>He was the British civil servant who played a major role in founding the INC in 1885.</t>
+          <t>Moderates strictly avoided violence.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Who started the newspaper 'Kesari'?</t>
+          <t>In which session was the demand for 'Swaraj' first made by INC?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Gopal Krishna Gokhale</t>
+          <t>1906 Calcutta</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Bipin Chandra Pal</t>
+          <t>1907 Surat</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Bal Gangadhar Tilak</t>
+          <t>1916 Lucknow</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Surendranath Banerjee</t>
+          <t>1920 Nagpur</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Bal Gangadhar Tilak</t>
+          <t>1906 Calcutta</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Used it to awaken political consciousness)</t>
+          <t>(Presided by Dadabhai Naoroji; Swaraj was formally adopted)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Which method was not used by the Moderates?</t>
+          <t>Which slogan is attributed to Bal Gangadhar Tilak?</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Petitions</t>
+          <t>Jai Hind</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Pamphlets</t>
+          <t>Inquilab Zindabad</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Prayers</t>
+          <t>Swaraj is my birthright and I shall have it</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Violent protests</t>
+          <t>Do or Die</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Violent protests</t>
+          <t>Swaraj is my birthright and I shall have it</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Moderates strictly avoided violence.</t>
+          <t>(Powerful assertion of self-rule)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Which newspaper was started by Bal Gangadhar Tilak?</t>
+          <t>The term 'Moderates' in Indian politics refers to?</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Kesari</t>
+          <t>Extremists</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>The Hindu</t>
+          <t>British loyalists</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Amrita Bazar Patrika</t>
+          <t>Early Nationalists</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Young India</t>
+          <t>Revolutionaries</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Kesari</t>
+          <t>Early Nationalists</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Tilak started ‘Kesari’ in Marathi to promote nationalism.</t>
+          <t>(They adopted peaceful and constitutional methods)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Which of the following was the main demand of early nationalists?</t>
+          <t>Which newspaper was started by Bal Gangadhar Tilak?</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Home Rule</t>
+          <t>Kesari</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Swaraj</t>
+          <t>The Hindu</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Dominion Status</t>
+          <t>Amrita Bazar Patrika</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Administrative and Economic Reforms</t>
+          <t>Young India</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Administrative and Economic Reforms</t>
+          <t>Kesari</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Early focus was on reforms, not independence)</t>
+          <t>Tilak started ‘Kesari’ in Marathi to promote nationalism.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Who among the following exposed the 'Drain of Wealth' theory?</t>
+          <t>What was a key criticism of the Moderates by Extremists?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Bal Gangadhar Tilak</t>
+          <t>Too radical</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Dadabhai Naoroji</t>
+          <t>Too elitist</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Gopal Krishna Gokhale</t>
+          <t>Too cooperative with British</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>M.G. Ranade</t>
+          <t>Too revolutionary</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dadabhai Naoroji</t>
+          <t>Too cooperative with British</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(He argued British rule drained India’s resources to Britain)</t>
+          <t>(They were seen as too soft and loyalist)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Who was called the 'Political Guru' of Gandhi?</t>
+          <t>Who is known as the 'Father of Indian Nationalism'?</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Tilak</t>
+          <t>Dadabhai Naoroji</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Nehru</t>
+          <t>Gopal Krishna Gokhale</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Gokhale</t>
+          <t>Bal Gangadhar Tilak</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lala Lajpat Rai</t>
+          <t>A.O. Hume</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Gokhale</t>
+          <t>Dadabhai Naoroji</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(He mentored Gandhi in his early political life)</t>
+          <t>(Recognized for pioneering efforts in forming INC and economic critique of British rule)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>The Indian Councils Act 1892 was passed during which phase of the Congress?</t>
+          <t>Who said: "The Congress is a microscopic minority"?</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Extremist</t>
+          <t>Lord Curzon</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Revolutionary</t>
+          <t>Lord Lytton</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Lord Ripon</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Post-Moderate</t>
+          <t>Lord Minto</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Lord Curzon</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>The act was a result of pressure from Moderate leaders.</t>
+          <t>(Justifying repressive measures and Bengal Partition)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Which of the following Moderate leaders was also a social reformer?</t>
+          <t>What was the main focus of early nationalism?</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Dadabhai Naoroji</t>
+          <t>Religious reforms</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Gokhale</t>
+          <t>Social service</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Tilak</t>
+          <t>Political reforms</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bipin Chandra Pal</t>
+          <t>Armed rebellion</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Gokhale</t>
+          <t>Political reforms</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Strong believer in social service and upliftment)</t>
+          <t>Moderates focused on constitutional and political demands.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Who founded the ‘Servants of India Society’?</t>
+          <t>Who started the newspaper 'Kesari'?</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Dadabhai Naoroji</t>
+          <t>Gopal Krishna Gokhale</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Gopal Krishna Gokhale</t>
+          <t>Bipin Chandra Pal</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Lala Lajpat Rai</t>
+          <t>Bal Gangadhar Tilak</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tilak</t>
+          <t>Surendranath Banerjee</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Gopal Krishna Gokhale</t>
+          <t>Bal Gangadhar Tilak</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>He founded it to train national workers.</t>
+          <t>(Used it to awaken political consciousness)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Which of the following was the main limitation of the Moderate phase?</t>
+          <t>Which session saw the demand for Swaraj for the first time?</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Lack of organization</t>
+          <t>1905 Banaras</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Use of violence</t>
+          <t>1906 Calcutta</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Support from peasants</t>
+          <t>1907 Surat</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Strong press</t>
+          <t>1916 Lucknow</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lack of organization</t>
+          <t>1906 Calcutta</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Their peaceful methods lacked mass mobilization.</t>
+          <t>This session under Dadabhai Naoroji declared Swaraj as the goal.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>The Age of Moderate Nationalism lasted from?</t>
+          <t>Who among the following exposed the 'Drain of Wealth' theory?</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>1885–1905</t>
+          <t>Bal Gangadhar Tilak</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1885–1915</t>
+          <t>Dadabhai Naoroji</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1905–1920</t>
+          <t>Gopal Krishna Gokhale</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>1885–1947</t>
+          <t>M.G. Ranade</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>1885–1905</t>
+          <t>Dadabhai Naoroji</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Before Extremist phase took over)</t>
+          <t>(He argued British rule drained India’s resources to Britain)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Who among these was both a Moderate and later associated with Gandhian politics?</t>
+          <t>Which of the following was the main demand of early nationalists?</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Tilak</t>
+          <t>Home Rule</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Naoroji</t>
+          <t>Swaraj</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Gokhale</t>
+          <t>Dominion Status</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bipin Chandra Pal</t>
+          <t>Administrative and Economic Reforms</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Gokhale</t>
+          <t>Administrative and Economic Reforms</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>He bridged the gap between Moderates and Gandhian politics.</t>
+          <t>(Early focus was on reforms, not independence)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>In which session was the demand for 'Swaraj' first made by INC?</t>
+          <t>The Indian National Congress was founded in which year?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>1906 Calcutta</t>
+          <t>1885</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1907 Surat</t>
+          <t>1895</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1916 Lucknow</t>
+          <t>1905</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>1920 Nagpur</t>
+          <t>1875</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>1906 Calcutta</t>
+          <t>1885</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Presided by Dadabhai Naoroji; Swaraj was formally adopted)</t>
+          <t>(Founded in 1885 by A.O. Hume to create a platform for civil and political dialogue)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Who presided over the first session of the Indian National Congress?</t>
+          <t>Which INC session was the last one led solely by Moderates?</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>A.O. Hume</t>
+          <t>1905 Banaras</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>W.C. Bonnerjee</t>
+          <t>1906 Calcutta</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Badruddin Tyabji</t>
+          <t>1907 Surat</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Surendranath Banerjee</t>
+          <t>1904 Bombay</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>W.C. Bonnerjee</t>
+          <t>1906 Calcutta</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Womesh Chunder Bonnerjee was the first president in Bombay session, 1885)</t>
+          <t>Next year the Surat Split occurred.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>The Indian National Congress was founded in which year?</t>
+          <t>Which Congress session saw the Moderates and Extremists split?</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>1885</t>
+          <t>1905</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1895</t>
+          <t>1906</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1905</t>
+          <t>1907</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>1875</t>
+          <t>1908</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>1885</t>
+          <t>1907</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Founded in 1885 by A.O. Hume to create a platform for civil and political dialogue)</t>
+          <t>(Split occurred at Surat session due to ideological differences)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Which Congress session saw the Moderates and Extremists split?</t>
+          <t>Which of the following was not a demand of the Moderates?</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>1905</t>
+          <t>Expansion of legislative councils</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1906</t>
+          <t>Separation of judiciary and executive</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1907</t>
+          <t>Complete independence</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>1908</t>
+          <t>Reduction in military expenditure</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>1907</t>
+          <t>Complete independence</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Split occurred at Surat session due to ideological differences)</t>
+          <t>Moderates sought reforms, not independence.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Who among the following was not a Moderate leader?</t>
+          <t>Which Moderate leader was known as the “Grand Old Man of India”?</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Surendranath Banerjee</t>
+          <t>Gokhale</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Gopal Krishna Gokhale</t>
+          <t>Dutt</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Bal Gangadhar Tilak</t>
+          <t>Naoroji</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>M.G. Ranade</t>
+          <t>Tilak</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Bal Gangadhar Tilak</t>
+          <t>Naoroji</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Tilak was a prominent extremist leader.</t>
+          <t>He was one of the oldest and most respected leaders.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Who said: "The Congress is a microscopic minority"?</t>
+          <t>Which British officer played a key role in the foundation of INC?</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Lord Curzon</t>
+          <t>Lord Ripon</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Lord Lytton</t>
+          <t>Lord Dufferin</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Lord Ripon</t>
+          <t>A.O. Hume</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lord Minto</t>
+          <t>Sir John Lawrence</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lord Curzon</t>
+          <t>A.O. Hume</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Justifying repressive measures and Bengal Partition)</t>
+          <t>(Retired ICS officer who helped Indians unite politically)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>What was the main focus of early nationalism?</t>
+          <t>Who among these was NOT a Moderate leader?</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Religious reforms</t>
+          <t>Dadabhai Naoroji</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Social service</t>
+          <t>Gopal Krishna Gokhale</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Political reforms</t>
+          <t>Lala Lajpat Rai</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Armed rebellion</t>
+          <t>W.C. Bonnerjee</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Political reforms</t>
+          <t>Lala Lajpat Rai</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Moderates focused on constitutional and political demands.</t>
+          <t>(He was part of the Extremist trio)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Who is known as the 'Father of Indian Nationalism'?</t>
+          <t>Who among the following was not a Moderate leader?</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Dadabhai Naoroji</t>
+          <t>Surendranath Banerjee</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2412,17 +2412,17 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>A.O. Hume</t>
+          <t>M.G. Ranade</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dadabhai Naoroji</t>
+          <t>Bal Gangadhar Tilak</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Recognized for pioneering efforts in forming INC and economic critique of British rule)</t>
+          <t>Tilak was a prominent extremist leader.</t>
         </is>
       </c>
     </row>

--- a/Data/MH_EarlyNationalism.xlsx
+++ b/Data/MH_EarlyNationalism.xlsx
@@ -472,41 +472,41 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Which of the following leaders is known as the 'Political Guru of Gandhi'?</t>
+          <t>Who among the following exposed the 'Drain of Wealth' theory?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Tilak</t>
+          <t>Bal Gangadhar Tilak</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Nehru</t>
+          <t>Dadabhai Naoroji</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Gokhale</t>
+          <t>Gopal Krishna Gokhale</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>R.C. Dutt</t>
+          <t>M.G. Ranade</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Gokhale</t>
+          <t>Dadabhai Naoroji</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Gandhi referred to Gokhale as his political mentor.</t>
+          <t>(He argued British rule drained India’s resources to Britain)</t>
         </is>
       </c>
     </row>
@@ -516,698 +516,702 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>The term “Economic Critique of British Imperialism” is associated with:</t>
+          <t>Which of the following was the main demand of early nationalists?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Extremists</t>
+          <t>Home Rule</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Moderates</t>
+          <t>Swaraj</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Revolutionaries</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
+          <t>Dominion Status</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Administrative and Economic Reforms</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Moderates</t>
+          <t>Administrative and Economic Reforms</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>They exposed British economic exploitation through data and speeches.</t>
+          <t>(Early focus was on reforms, not independence)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Who among these was both a Moderate and later associated with Gandhian politics?</t>
+          <t>The Indian National Congress was founded in which year?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Tilak</t>
+          <t>1885</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Naoroji</t>
+          <t>1895</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Gokhale</t>
+          <t>1905</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bipin Chandra Pal</t>
+          <t>1875</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Gokhale</t>
+          <t>1885</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>He bridged the gap between Moderates and Gandhian politics.</t>
+          <t>(Founded in 1885 by A.O. Hume to create a platform for civil and political dialogue)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Which book was written by Dadabhai Naoroji on economic drain?</t>
+          <t>Which INC session was the last one led solely by Moderates?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>India Divided</t>
+          <t>1905 Banaras</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Poverty and Un-British Rule in India</t>
+          <t>1906 Calcutta</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>The Problem of India</t>
+          <t>1907 Surat</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Economic History of India</t>
+          <t>1904 Bombay</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poverty and Un-British Rule in India</t>
+          <t>1906 Calcutta</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Seminal work explaining British economic exploitation)</t>
+          <t>Next year the Surat Split occurred.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Who among the following founded the 'Servants of India Society'?</t>
+          <t>Which Congress session saw the Moderates and Extremists split?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Dadabhai Naoroji</t>
+          <t>1905</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Gopal Krishna Gokhale</t>
+          <t>1906</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tilak</t>
+          <t>1907</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>D.E. Wacha</t>
+          <t>1908</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Gopal Krishna Gokhale</t>
+          <t>1907</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Founded in 1905 for education and social service)</t>
+          <t>(Split occurred at Surat session due to ideological differences)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Which event led to the rise of Extremist politics?</t>
+          <t>Which of the following was not a demand of the Moderates?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Partition of Bengal</t>
+          <t>Expansion of legislative councils</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Swadeshi Movement</t>
+          <t>Separation of judiciary and executive</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Rowlatt Act</t>
+          <t>Complete independence</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Simon Commission</t>
+          <t>Reduction in military expenditure</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Partition of Bengal</t>
+          <t>Complete independence</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>It was the spark that turned public sentiment radical.</t>
+          <t>Moderates sought reforms, not independence.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Who presided over the first session of the Indian National Congress?</t>
+          <t>Which Moderate leader was known as the “Grand Old Man of India”?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>A.O. Hume</t>
+          <t>Gokhale</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>W.C. Bonnerjee</t>
+          <t>Dutt</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Badruddin Tyabji</t>
+          <t>Naoroji</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Surendranath Banerjee</t>
+          <t>Tilak</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>W.C. Bonnerjee</t>
+          <t>Naoroji</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Womesh Chunder Bonnerjee was the first president in Bombay session, 1885)</t>
+          <t>He was one of the oldest and most respected leaders.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Which of the following Moderate leaders was also a social reformer?</t>
+          <t>Which British officer played a key role in the foundation of INC?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Dadabhai Naoroji</t>
+          <t>Lord Ripon</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Gokhale</t>
+          <t>Lord Dufferin</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tilak</t>
+          <t>A.O. Hume</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bipin Chandra Pal</t>
+          <t>Sir John Lawrence</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Gokhale</t>
+          <t>A.O. Hume</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Strong believer in social service and upliftment)</t>
+          <t>(Retired ICS officer who helped Indians unite politically)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>The trio of Lal-Bal-Pal belonged to which group?</t>
+          <t>Who among these was NOT a Moderate leader?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Moderates</t>
+          <t>Dadabhai Naoroji</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Extremists</t>
+          <t>Gopal Krishna Gokhale</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Revolutionaries</t>
+          <t>Lala Lajpat Rai</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Socialists</t>
+          <t>W.C. Bonnerjee</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Extremists</t>
+          <t>Lala Lajpat Rai</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Assertive nationalists for self-rule)</t>
+          <t>(He was part of the Extremist trio)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Who said “The Congress is in reality a civil war without arms”?</t>
+          <t>Who among the following was not a Moderate leader?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Lala Lajpat Rai</t>
+          <t>Surendranath Banerjee</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Tilak</t>
+          <t>Gopal Krishna Gokhale</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Lord Curzon</t>
+          <t>Bal Gangadhar Tilak</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gokhale</t>
+          <t>M.G. Ranade</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lord Curzon</t>
+          <t>Bal Gangadhar Tilak</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>He criticized the Congress for creating unrest.</t>
+          <t>Tilak was a prominent extremist leader.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Who coined the term "Drain of Wealth"?</t>
+          <t>In which session was the demand for 'Swaraj' first made by INC?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>A.O. Hume</t>
+          <t>1906 Calcutta</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>R.C. Dutt</t>
+          <t>1907 Surat</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Gopal Krishna Gokhale</t>
+          <t>1916 Lucknow</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dadabhai Naoroji</t>
+          <t>1920 Nagpur</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dadabhai Naoroji</t>
+          <t>1906 Calcutta</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>He explained how British economic policies led to economic exploitation of India.</t>
+          <t>(Presided by Dadabhai Naoroji; Swaraj was formally adopted)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Who founded the ‘Servants of India Society’?</t>
+          <t>Which slogan is attributed to Bal Gangadhar Tilak?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Dadabhai Naoroji</t>
+          <t>Jai Hind</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Gopal Krishna Gokhale</t>
+          <t>Inquilab Zindabad</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Lala Lajpat Rai</t>
+          <t>Swaraj is my birthright and I shall have it</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tilak</t>
+          <t>Do or Die</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Gopal Krishna Gokhale</t>
+          <t>Swaraj is my birthright and I shall have it</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>He founded it to train national workers.</t>
+          <t>(Powerful assertion of self-rule)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Who wrote the book ‘Poverty and Un-British Rule in India’?</t>
+          <t>The term 'Moderates' in Indian politics refers to?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Gokhale</t>
+          <t>Extremists</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Naoroji</t>
+          <t>British loyalists</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dutt</t>
+          <t>Early Nationalists</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Banerjee</t>
+          <t>Revolutionaries</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Naoroji</t>
+          <t>Early Nationalists</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>It argued that British policies were causing Indian poverty.</t>
+          <t>(They adopted peaceful and constitutional methods)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Which act led to the partition of Bengal in 1905?</t>
+          <t>Which newspaper was started by Bal Gangadhar Tilak?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Indian Councils Act 1892</t>
+          <t>Kesari</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Morley-Minto Reforms</t>
+          <t>The Hindu</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Act of 1905</t>
+          <t>Amrita Bazar Patrika</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>There was no such act</t>
+          <t>Young India</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>There was no such act</t>
+          <t>Kesari</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Partition was done through executive action by Lord Curzon)</t>
+          <t>Tilak started ‘Kesari’ in Marathi to promote nationalism.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>In which year did the Moderate Phase of the Indian National Congress end?</t>
+          <t>What was a key criticism of the Moderates by Extremists?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>Too radical</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1905</t>
+          <t>Too elitist</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1910</t>
+          <t>Too cooperative with British</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1915</t>
+          <t>Too revolutionary</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1905</t>
+          <t>Too cooperative with British</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>The Moderates dominated until the partition of Bengal in 1905, which sparked extremist action.</t>
+          <t>(They were seen as too soft and loyalist)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Who was elected President of INC in 1907 Surat session?</t>
+          <t>Who is known as the 'Father of Indian Nationalism'?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Tilak</t>
+          <t>Dadabhai Naoroji</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Lajpat Rai</t>
+          <t>Gopal Krishna Gokhale</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Rash Behari Bose</t>
+          <t>Bal Gangadhar Tilak</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rash Behari Ghosh</t>
+          <t>A.O. Hume</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rash Behari Ghosh</t>
+          <t>Dadabhai Naoroji</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Moderates chose him, leading to split)</t>
+          <t>(Recognized for pioneering efforts in forming INC and economic critique of British rule)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Who among the following gave the slogan “Self-government is our birthright”?</t>
+          <t>Who said: "The Congress is a microscopic minority"?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Dadabhai Naoroji</t>
+          <t>Lord Curzon</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Gopal Krishna Gokhale</t>
+          <t>Lord Lytton</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>B.G. Tilak</t>
+          <t>Lord Ripon</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>R.C. Dutt</t>
+          <t>Lord Minto</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>B.G. Tilak</t>
+          <t>Lord Curzon</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>This slogan was associated with the extremist movement.</t>
+          <t>(Justifying repressive measures and Bengal Partition)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Which of the following was the main limitation of the Moderate phase?</t>
+          <t>What was the main focus of early nationalism?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Lack of organization</t>
+          <t>Religious reforms</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Use of violence</t>
+          <t>Social service</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Support from peasants</t>
+          <t>Political reforms</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Strong press</t>
+          <t>Armed rebellion</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lack of organization</t>
+          <t>Political reforms</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Their peaceful methods lacked mass mobilization.</t>
+          <t>Moderates focused on constitutional and political demands.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Who is considered the father of Indian National Congress?</t>
+          <t>Who started the newspaper 'Kesari'?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>A.O. Hume</t>
+          <t>Gopal Krishna Gokhale</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Dadabhai Naoroji</t>
+          <t>Bipin Chandra Pal</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Gopal Krishna Gokhale</t>
+          <t>Bal Gangadhar Tilak</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1217,302 +1221,302 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>A.O. Hume</t>
+          <t>Bal Gangadhar Tilak</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>He was the British civil servant who played a major role in founding the INC in 1885.</t>
+          <t>(Used it to awaken political consciousness)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Which of these demands was first raised by the Moderates?</t>
+          <t>Which session saw the demand for Swaraj for the first time?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Swaraj</t>
+          <t>1905 Banaras</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Universal Adult Franchise</t>
+          <t>1906 Calcutta</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Indianisation of Civil Services</t>
+          <t>1907 Surat</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Boycott of British Goods</t>
+          <t>1916 Lucknow</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Indianisation of Civil Services</t>
+          <t>1906 Calcutta</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Moderates demanded ICS entry for Indians.</t>
+          <t>This session under Dadabhai Naoroji declared Swaraj as the goal.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>What was the main objective of the early nationalists?</t>
+          <t>Which of these demands was first raised by the Moderates?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Complete Independence</t>
+          <t>Swaraj</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Armed Revolution</t>
+          <t>Universal Adult Franchise</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Constitutional Reforms</t>
+          <t>Indianisation of Civil Services</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Social Reforms</t>
+          <t>Boycott of British Goods</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Constitutional Reforms</t>
+          <t>Indianisation of Civil Services</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(They believed in gradual reforms and dialogue)</t>
+          <t>Moderates demanded ICS entry for Indians.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>The Age of Moderate Nationalism lasted from?</t>
+          <t>What was the main objective of the early nationalists?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1885–1905</t>
+          <t>Complete Independence</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1885–1915</t>
+          <t>Armed Revolution</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1905–1920</t>
+          <t>Constitutional Reforms</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1885–1947</t>
+          <t>Social Reforms</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1885–1905</t>
+          <t>Constitutional Reforms</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Before Extremist phase took over)</t>
+          <t>(They believed in gradual reforms and dialogue)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Who was called the 'Political Guru' of Gandhi?</t>
+          <t>The Age of Moderate Nationalism lasted from?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Tilak</t>
+          <t>1885–1905</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Nehru</t>
+          <t>1885–1915</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Gokhale</t>
+          <t>1905–1920</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lala Lajpat Rai</t>
+          <t>1885–1947</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Gokhale</t>
+          <t>1885–1905</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(He mentored Gandhi in his early political life)</t>
+          <t>(Before Extremist phase took over)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Which newspaper was started by Gokhale to voice nationalist ideas?</t>
+          <t>Who was called the 'Political Guru' of Gandhi?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>The Hindu</t>
+          <t>Tilak</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>The Leader</t>
+          <t>Nehru</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>The Times of India</t>
+          <t>Gokhale</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Young India</t>
+          <t>Lala Lajpat Rai</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>The Leader</t>
+          <t>Gokhale</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(He used it to advocate reforms and educate people)</t>
+          <t>(He mentored Gandhi in his early political life)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Which session of the INC was presided over by Dadabhai Naoroji for the first time?</t>
+          <t>Which newspaper was started by Gokhale to voice nationalist ideas?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Bombay 1885</t>
+          <t>The Hindu</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Calcutta 1886</t>
+          <t>The Leader</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Madras 1887</t>
+          <t>The Times of India</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Allahabad 1888</t>
+          <t>Young India</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Calcutta 1886</t>
+          <t>The Leader</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Dadabhai Naoroji presided over the second session of INC in 1886.</t>
+          <t>(He used it to advocate reforms and educate people)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>The newspaper “The Hindu” was initially supportive of which phase?</t>
+          <t>Which session of the INC was presided over by Dadabhai Naoroji for the first time?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Extremist</t>
+          <t>Bombay 1885</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Calcutta 1886</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Revolutionary</t>
+          <t>Madras 1887</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gandhian</t>
+          <t>Allahabad 1888</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Calcutta 1886</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>It published articles supporting early nationalist demands.</t>
+          <t>Dadabhai Naoroji presided over the second session of INC in 1886.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>The Indian Councils Act 1892 was passed during which phase of the Congress?</t>
+          <t>The newspaper “The Hindu” was initially supportive of which phase?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1522,387 +1526,387 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
           <t>Revolutionary</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Gandhian</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Post-Moderate</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>The act was a result of pressure from Moderate leaders.</t>
+          <t>It published articles supporting early nationalist demands.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>What was the venue of the second session of the Indian National Congress?</t>
+          <t>The Indian Councils Act 1892 was passed during which phase of the Congress?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Bombay</t>
+          <t>Extremist</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Madras</t>
+          <t>Revolutionary</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Calcutta</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Allahabad</t>
+          <t>Post-Moderate</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Calcutta</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Held in 1886 and presided over by Dadabhai Naoroji)</t>
+          <t>The act was a result of pressure from Moderate leaders.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Which method was not used by the Moderates?</t>
+          <t>What was the venue of the second session of the Indian National Congress?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Petitions</t>
+          <t>Bombay</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Pamphlets</t>
+          <t>Madras</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Prayers</t>
+          <t>Calcutta</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Violent protests</t>
+          <t>Allahabad</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Violent protests</t>
+          <t>Calcutta</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Moderates strictly avoided violence.</t>
+          <t>(Held in 1886 and presided over by Dadabhai Naoroji)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>In which session was the demand for 'Swaraj' first made by INC?</t>
+          <t>Which method was not used by the Moderates?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1906 Calcutta</t>
+          <t>Petitions</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1907 Surat</t>
+          <t>Pamphlets</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1916 Lucknow</t>
+          <t>Prayers</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1920 Nagpur</t>
+          <t>Violent protests</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>1906 Calcutta</t>
+          <t>Violent protests</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Presided by Dadabhai Naoroji; Swaraj was formally adopted)</t>
+          <t>Moderates strictly avoided violence.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Which slogan is attributed to Bal Gangadhar Tilak?</t>
+          <t>Who said “The Congress is in reality a civil war without arms”?</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Jai Hind</t>
+          <t>Lala Lajpat Rai</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Inquilab Zindabad</t>
+          <t>Tilak</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Swaraj is my birthright and I shall have it</t>
+          <t>Lord Curzon</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Do or Die</t>
+          <t>Gokhale</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Swaraj is my birthright and I shall have it</t>
+          <t>Lord Curzon</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Powerful assertion of self-rule)</t>
+          <t>He criticized the Congress for creating unrest.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>The term 'Moderates' in Indian politics refers to?</t>
+          <t>Who coined the term "Drain of Wealth"?</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Extremists</t>
+          <t>A.O. Hume</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>British loyalists</t>
+          <t>R.C. Dutt</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Early Nationalists</t>
+          <t>Gopal Krishna Gokhale</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Revolutionaries</t>
+          <t>Dadabhai Naoroji</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Early Nationalists</t>
+          <t>Dadabhai Naoroji</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(They adopted peaceful and constitutional methods)</t>
+          <t>He explained how British economic policies led to economic exploitation of India.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Which newspaper was started by Bal Gangadhar Tilak?</t>
+          <t>Who founded the ‘Servants of India Society’?</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Kesari</t>
+          <t>Dadabhai Naoroji</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>The Hindu</t>
+          <t>Gopal Krishna Gokhale</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Amrita Bazar Patrika</t>
+          <t>Lala Lajpat Rai</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Young India</t>
+          <t>Tilak</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Kesari</t>
+          <t>Gopal Krishna Gokhale</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Tilak started ‘Kesari’ in Marathi to promote nationalism.</t>
+          <t>He founded it to train national workers.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>What was a key criticism of the Moderates by Extremists?</t>
+          <t>Who wrote the book ‘Poverty and Un-British Rule in India’?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Too radical</t>
+          <t>Gokhale</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Too elitist</t>
+          <t>Naoroji</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Too cooperative with British</t>
+          <t>Dutt</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Too revolutionary</t>
+          <t>Banerjee</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Too cooperative with British</t>
+          <t>Naoroji</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(They were seen as too soft and loyalist)</t>
+          <t>It argued that British policies were causing Indian poverty.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Who is known as the 'Father of Indian Nationalism'?</t>
+          <t>Which act led to the partition of Bengal in 1905?</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Dadabhai Naoroji</t>
+          <t>Indian Councils Act 1892</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Gopal Krishna Gokhale</t>
+          <t>Morley-Minto Reforms</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bal Gangadhar Tilak</t>
+          <t>Act of 1905</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>A.O. Hume</t>
+          <t>There was no such act</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dadabhai Naoroji</t>
+          <t>There was no such act</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Recognized for pioneering efforts in forming INC and economic critique of British rule)</t>
+          <t>(Partition was done through executive action by Lord Curzon)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Who said: "The Congress is a microscopic minority"?</t>
+          <t>In which year did the Moderate Phase of the Indian National Congress end?</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Lord Curzon</t>
+          <t>1900</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Lord Lytton</t>
+          <t>1905</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Lord Ripon</t>
+          <t>1910</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lord Minto</t>
+          <t>1915</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lord Curzon</t>
+          <t>1905</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Justifying repressive measures and Bengal Partition)</t>
+          <t>The Moderates dominated until the partition of Bengal in 1905, which sparked extremist action.</t>
         </is>
       </c>
     </row>
@@ -1912,132 +1916,132 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>What was the main focus of early nationalism?</t>
+          <t>Who was elected President of INC in 1907 Surat session?</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Religious reforms</t>
+          <t>Tilak</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Social service</t>
+          <t>Lajpat Rai</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Political reforms</t>
+          <t>Rash Behari Bose</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Armed rebellion</t>
+          <t>Rash Behari Ghosh</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Political reforms</t>
+          <t>Rash Behari Ghosh</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Moderates focused on constitutional and political demands.</t>
+          <t>(Moderates chose him, leading to split)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Who started the newspaper 'Kesari'?</t>
+          <t>Who among the following gave the slogan “Self-government is our birthright”?</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
+          <t>Dadabhai Naoroji</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
           <t>Gopal Krishna Gokhale</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Bipin Chandra Pal</t>
-        </is>
-      </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bal Gangadhar Tilak</t>
+          <t>B.G. Tilak</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Surendranath Banerjee</t>
+          <t>R.C. Dutt</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Bal Gangadhar Tilak</t>
+          <t>B.G. Tilak</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Used it to awaken political consciousness)</t>
+          <t>This slogan was associated with the extremist movement.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Which session saw the demand for Swaraj for the first time?</t>
+          <t>Which of the following was the main limitation of the Moderate phase?</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>1905 Banaras</t>
+          <t>Lack of organization</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1906 Calcutta</t>
+          <t>Use of violence</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1907 Surat</t>
+          <t>Support from peasants</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>1916 Lucknow</t>
+          <t>Strong press</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>1906 Calcutta</t>
+          <t>Lack of organization</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>This session under Dadabhai Naoroji declared Swaraj as the goal.</t>
+          <t>Their peaceful methods lacked mass mobilization.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Who among the following exposed the 'Drain of Wealth' theory?</t>
+          <t>Who is considered the father of Indian National Congress?</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Bal Gangadhar Tilak</t>
+          <t>A.O. Hume</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2052,307 +2056,303 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>M.G. Ranade</t>
+          <t>Surendranath Banerjee</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dadabhai Naoroji</t>
+          <t>A.O. Hume</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(He argued British rule drained India’s resources to Britain)</t>
+          <t>He was the British civil servant who played a major role in founding the INC in 1885.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Which of the following was the main demand of early nationalists?</t>
+          <t>Which of the following leaders is known as the 'Political Guru of Gandhi'?</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Home Rule</t>
+          <t>Tilak</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Swaraj</t>
+          <t>Nehru</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Dominion Status</t>
+          <t>Gokhale</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Administrative and Economic Reforms</t>
+          <t>R.C. Dutt</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Administrative and Economic Reforms</t>
+          <t>Gokhale</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Early focus was on reforms, not independence)</t>
+          <t>Gandhi referred to Gokhale as his political mentor.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>The Indian National Congress was founded in which year?</t>
+          <t>The term “Economic Critique of British Imperialism” is associated with:</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>1885</t>
+          <t>Extremists</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1895</t>
+          <t>Moderates</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1905</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>1875</t>
-        </is>
-      </c>
+          <t>Revolutionaries</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>1885</t>
+          <t>Moderates</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Founded in 1885 by A.O. Hume to create a platform for civil and political dialogue)</t>
+          <t>They exposed British economic exploitation through data and speeches.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Which INC session was the last one led solely by Moderates?</t>
+          <t>Who among these was both a Moderate and later associated with Gandhian politics?</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>1905 Banaras</t>
+          <t>Tilak</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1906 Calcutta</t>
+          <t>Naoroji</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1907 Surat</t>
+          <t>Gokhale</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>1904 Bombay</t>
+          <t>Bipin Chandra Pal</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>1906 Calcutta</t>
+          <t>Gokhale</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Next year the Surat Split occurred.</t>
+          <t>He bridged the gap between Moderates and Gandhian politics.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Which Congress session saw the Moderates and Extremists split?</t>
+          <t>Which book was written by Dadabhai Naoroji on economic drain?</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>1905</t>
+          <t>India Divided</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1906</t>
+          <t>Poverty and Un-British Rule in India</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1907</t>
+          <t>The Problem of India</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>1908</t>
+          <t>Economic History of India</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>1907</t>
+          <t>Poverty and Un-British Rule in India</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Split occurred at Surat session due to ideological differences)</t>
+          <t>(Seminal work explaining British economic exploitation)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Which of the following was not a demand of the Moderates?</t>
+          <t>Who among the following founded the 'Servants of India Society'?</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Expansion of legislative councils</t>
+          <t>Dadabhai Naoroji</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Separation of judiciary and executive</t>
+          <t>Gopal Krishna Gokhale</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Complete independence</t>
+          <t>Tilak</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Reduction in military expenditure</t>
+          <t>D.E. Wacha</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Complete independence</t>
+          <t>Gopal Krishna Gokhale</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Moderates sought reforms, not independence.</t>
+          <t>(Founded in 1905 for education and social service)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Which Moderate leader was known as the “Grand Old Man of India”?</t>
+          <t>Which event led to the rise of Extremist politics?</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Gokhale</t>
+          <t>Partition of Bengal</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Dutt</t>
+          <t>Swadeshi Movement</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Naoroji</t>
+          <t>Rowlatt Act</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tilak</t>
+          <t>Simon Commission</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Naoroji</t>
+          <t>Partition of Bengal</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>He was one of the oldest and most respected leaders.</t>
+          <t>It was the spark that turned public sentiment radical.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Which British officer played a key role in the foundation of INC?</t>
+          <t>Who presided over the first session of the Indian National Congress?</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Lord Ripon</t>
+          <t>A.O. Hume</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Lord Dufferin</t>
+          <t>W.C. Bonnerjee</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>A.O. Hume</t>
+          <t>Badruddin Tyabji</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Sir John Lawrence</t>
+          <t>Surendranath Banerjee</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>A.O. Hume</t>
+          <t>W.C. Bonnerjee</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Retired ICS officer who helped Indians unite politically)</t>
+          <t>(Womesh Chunder Bonnerjee was the first president in Bombay session, 1885)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Who among these was NOT a Moderate leader?</t>
+          <t>Which of the following Moderate leaders was also a social reformer?</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2362,67 +2362,67 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Gopal Krishna Gokhale</t>
+          <t>Gokhale</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Lala Lajpat Rai</t>
+          <t>Tilak</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>W.C. Bonnerjee</t>
+          <t>Bipin Chandra Pal</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lala Lajpat Rai</t>
+          <t>Gokhale</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(He was part of the Extremist trio)</t>
+          <t>(Strong believer in social service and upliftment)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Who among the following was not a Moderate leader?</t>
+          <t>The trio of Lal-Bal-Pal belonged to which group?</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Surendranath Banerjee</t>
+          <t>Moderates</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Gopal Krishna Gokhale</t>
+          <t>Extremists</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Bal Gangadhar Tilak</t>
+          <t>Revolutionaries</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>M.G. Ranade</t>
+          <t>Socialists</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Bal Gangadhar Tilak</t>
+          <t>Extremists</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Tilak was a prominent extremist leader.</t>
+          <t>(Assertive nationalists for self-rule)</t>
         </is>
       </c>
     </row>
